--- a/models/LOSCAR_sheets/LOSCAR_sheets.xlsx
+++ b/models/LOSCAR_sheets/LOSCAR_sheets.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="94">
   <si>
     <t xml:space="preserve">This workbook contains model configuration information used to initialize the LOSCAR model within ESBMTK. </t>
   </si>
@@ -107,6 +107,9 @@
     <t xml:space="preserve">[chemical species]: Initial concentration of the specified species (in umol/lg). Column names must match species names defined in the model. </t>
   </si>
   <si>
+    <t xml:space="preserve">delta_[chemical species]: Initial isotope ratio of the specified species (optional)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Column names: transport_matrix</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
     <t xml:space="preserve">species_ppm: initial concentration of the gas species. May be specified in ppm or percent (e.g.: 280 ppm; e.g.: 21 percent)</t>
   </si>
   <si>
+    <t xml:space="preserve">delta_[gaseous species]: Initial isotope ratio of the specified species in the gas reservoir (optional). Note that no value should be entered for species for which isotopes are not enabled.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Column names: gas_exchange</t>
   </si>
   <si>
@@ -182,6 +188,9 @@
     <t xml:space="preserve">O2</t>
   </si>
   <si>
+    <t xml:space="preserve">delta_DIC</t>
+  </si>
+  <si>
     <t xml:space="preserve">A_sb</t>
   </si>
   <si>
@@ -240,6 +249,9 @@
   </si>
   <si>
     <t xml:space="preserve">species_ppm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">delta</t>
   </si>
   <si>
     <t xml:space="preserve">CO2_At</t>
@@ -326,6 +338,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -357,14 +370,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -437,11 +449,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -453,19 +469,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -608,7 +620,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A41"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="11.53"/>
@@ -644,7 +656,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
@@ -719,13 +731,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -744,44 +756,54 @@
         <v>25</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>31</v>
+      <c r="A39" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -800,566 +822,622 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9.625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="14.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="10.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="13.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="21.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="3" width="17.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="3" width="13.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="3" width="9.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="3" width="7.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="14.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="10.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="4" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="21.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="4" width="17.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="4" width="13.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="4" width="9.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="4" width="7.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3" t="n">
+      <c r="A2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J2" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>200</v>
       </c>
+      <c r="M2" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="A3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="J3" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>200</v>
       </c>
+      <c r="M3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C4" s="3" t="n">
+      <c r="A4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="H4" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J4" s="3" t="n">
+      <c r="J4" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>200</v>
       </c>
+      <c r="M4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>-6500</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.26</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="F5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="G5" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="H5" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3" t="n">
+      <c r="I5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G6" s="3" t="n">
+      <c r="G6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="H6" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J6" s="3" t="n">
+      <c r="J6" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="3" t="n">
+      <c r="M6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G7" s="3" t="n">
+      <c r="G7" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="H7" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J7" s="3" t="n">
+      <c r="J7" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="3" t="n">
+      <c r="M7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="E8" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="F8" s="3" t="n">
+      <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="3" t="n">
+      <c r="G8" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="H8" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J8" s="3" t="n">
+      <c r="J8" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="3" t="n">
+      <c r="M8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="D9" s="4" t="n">
         <v>-6500</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="E9" s="4" t="n">
         <v>0.18</v>
       </c>
-      <c r="F9" s="3" t="n">
+      <c r="F9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="3" t="n">
+      <c r="G9" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H9" s="3" t="n">
+      <c r="H9" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G10" s="3" t="n">
+      <c r="G10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H10" s="3" t="n">
+      <c r="H10" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J10" s="3" t="n">
+      <c r="J10" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K10" s="3" t="n">
+      <c r="K10" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="3" t="n">
+      <c r="M10" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>-100</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="E11" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="F11" s="3" t="n">
+      <c r="F11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G11" s="3" t="n">
+      <c r="G11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="H11" s="3" t="n">
+      <c r="H11" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J11" s="3" t="n">
+      <c r="J11" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="3" t="n">
+      <c r="M11" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="n">
         <v>-1000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="E12" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="F12" s="3" t="n">
+      <c r="F12" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="3" t="n">
+      <c r="G12" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H12" s="3" t="n">
+      <c r="H12" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J12" s="3" t="n">
+      <c r="J12" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C13" s="3" t="n">
+      <c r="M12" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>-6000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="4" t="n">
         <v>-6500</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="E13" s="4" t="n">
         <v>0.46</v>
       </c>
-      <c r="F13" s="3" t="n">
+      <c r="F13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="3" t="n">
+      <c r="G13" s="4" t="n">
         <v>240</v>
       </c>
-      <c r="H13" s="3" t="n">
+      <c r="H13" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="3" t="n">
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>-250</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="E14" s="4" t="n">
         <v>0.1</v>
       </c>
-      <c r="F14" s="3" t="n">
+      <c r="F14" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="3" t="n">
+      <c r="G14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="H14" s="3" t="n">
+      <c r="H14" s="4" t="n">
         <v>34.7</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="4" t="n">
         <v>2210</v>
       </c>
-      <c r="J14" s="3" t="n">
+      <c r="J14" s="4" t="n">
         <v>2310</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="4" t="n">
         <v>2.1</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>200</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="4" t="s">
+      <c r="M14" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="N14" s="4"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="5" t="s">
         <v>63</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1395,71 +1473,75 @@
   <dimension ref="A1:G5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="3" width="15.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="4" width="15.29"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="7"/>
+      <c r="A1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" s="8"/>
+        <v>72</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" s="8"/>
       <c r="F2" s="8"/>
-      <c r="G2" s="7"/>
+      <c r="G2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="7"/>
+        <v>74</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="8"/>
       <c r="F3" s="8"/>
-      <c r="G3" s="7"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="8"/>
-      <c r="G4" s="7"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="A5" s="5"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1480,233 +1562,233 @@
   <dimension ref="A1:D17"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="12.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="12.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="15.72"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1718,7 +1800,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A2:B16" type="list">
-      <formula1>"H_sb, A_sb, A_ib,A_db,I_sb,I_ib,I_db,P_sb,P_ib,P_db"</formula1>
+      <formula1>"H_sb,A_sb,A_ib,A_db,I_sb,I_ib,I_db,P_sb,P_ib,P_db"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C2:C16" type="list">
@@ -1744,40 +1826,42 @@
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="20.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="13.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="22.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="16.48"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>87</v>
+        <v>67</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>89</v>
+      <c r="A2" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
-        <v>45</v>
+      <c r="A3" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
